--- a/artfynd/A 785-2024 artfynd.xlsx
+++ b/artfynd/A 785-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067030</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>131067033</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 785-2024 artfynd.xlsx
+++ b/artfynd/A 785-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067030</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>131067033</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 785-2024 artfynd.xlsx
+++ b/artfynd/A 785-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067030</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131067005</v>
       </c>
       <c r="B3" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>131067033</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131067006</v>
       </c>
       <c r="B5" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 785-2024 artfynd.xlsx
+++ b/artfynd/A 785-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067030</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131067005</v>
       </c>
       <c r="B3" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>131067033</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131067006</v>
       </c>
       <c r="B5" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 785-2024 artfynd.xlsx
+++ b/artfynd/A 785-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067030</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>131067033</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 785-2024 artfynd.xlsx
+++ b/artfynd/A 785-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131067030</v>
+        <v>131067032</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466302</v>
+        <v>466239</v>
       </c>
       <c r="R2" t="n">
-        <v>7046517</v>
+        <v>7046392</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -801,57 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067005</v>
+        <v>131067033</v>
       </c>
       <c r="B3" t="n">
-        <v>57076</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466351</v>
+        <v>466193</v>
       </c>
       <c r="R3" t="n">
-        <v>7046569</v>
+        <v>7046386</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +879,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,12 +888,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -920,14 +912,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067033</v>
+        <v>131067035</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -958,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466193</v>
+        <v>466172</v>
       </c>
       <c r="R4" t="n">
-        <v>7046386</v>
+        <v>7046340</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +990,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1005,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1031,57 +1043,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067006</v>
+        <v>131067036</v>
       </c>
       <c r="B5" t="n">
-        <v>57076</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466180</v>
+        <v>466113</v>
       </c>
       <c r="R5" t="n">
-        <v>7046368</v>
+        <v>7046326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,12 +1130,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1147,6 +1171,1114 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131067451</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Åbogen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>466178</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7046388</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gran, någon bål</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131067452</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åbogen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>466252</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7046439</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131067453</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Åbogen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>466258</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7046494</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131067000</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långan Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>466110</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7046316</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131067781</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långan Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>466204</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7046448</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131067803</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långan Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>466227</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7046368</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131067006</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långan Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>466180</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7046368</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131067030</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långan Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>466302</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7046517</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131067005</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långan Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>466351</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7046569</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 785-2024 artfynd.xlsx
+++ b/artfynd/A 785-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067030</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067032</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067033</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067035</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067036</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1409,6 +1439,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067451</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1525,6 +1560,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067452</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1641,6 +1681,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067453</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1776,6 +1821,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067000</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1906,6 +1956,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067781</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2041,6 +2096,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067803</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2160,6 +2220,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067005</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2279,8 +2344,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067006</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>